--- a/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
+++ b/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="232">
   <si>
     <t>Notes</t>
   </si>
@@ -736,6 +736,9 @@
   </si>
   <si>
     <t>Sat Nov 15 20:48:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 19 09:48:51 EST 2025</t>
   </si>
 </sst>
 </file>
@@ -2445,7 +2448,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>

--- a/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
+++ b/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="269">
   <si>
     <t>Notes</t>
   </si>
@@ -739,6 +739,117 @@
   </si>
   <si>
     <t>Fri Dec 19 09:48:51 EST 2025</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:07:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:09:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:11:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:12:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:13:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:17:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:18:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:19:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:20:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:21:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:22:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:24:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:32:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:35:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:42:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:44:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:46:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:47:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:48:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:49:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:51:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:52:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:55:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:03:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:21:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:23:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:25:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:26:28 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1353,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -1278,7 +1389,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -1313,7 +1424,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -1348,7 +1459,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2182,10 +2293,10 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2218,10 +2329,10 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2256,7 +2367,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2288,10 +2399,10 @@
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2448,7 +2559,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2484,7 +2595,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2519,7 +2630,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2554,7 +2665,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2879,7 +2990,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>111</v>
@@ -2921,7 +3032,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>112</v>
@@ -3483,7 +3594,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -3635,7 +3746,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>

--- a/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
+++ b/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloned-Project-Katalon\VPS-Katalon\KatalonData\IWPTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{BC6F2250-260E-43BA-A2DF-82E583B86DBD}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{4E725288-5BBA-4857-9DFD-BBBB1B98FCE6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="10" firstSheet="1" windowHeight="16920" windowWidth="30960" xWindow="-120" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}" yWindow="-120"/>
+    <workbookView activeTab="2" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{19E085DA-5ADF-4B16-9D78-B410FD3FCE3D}" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowCC" r:id="rId1" sheetId="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="220">
   <si>
     <t>Notes</t>
   </si>
@@ -528,42 +528,6 @@
     <t>824</t>
   </si>
   <si>
-    <t>Wed Aug 28 22:55:42 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed Aug 28 22:56:29 EDT 2024</t>
-  </si>
-  <si>
-    <t>Wed Aug 28 23:11:55 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:16:47 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:17:58 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:19:07 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:20:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:25:15 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:26:26 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:27:34 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:28:41 EDT 2024</t>
-  </si>
-  <si>
-    <t>Thu Aug 29 20:35:49 EDT 2024</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -579,277 +543,166 @@
     <t>ExpY</t>
   </si>
   <si>
-    <t>Tue Jan 21 17:01:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:02:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:03:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:04:37 EST 2025</t>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:42:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:44:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:45:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:51:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:52:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 14:55:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:03:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 15:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:21:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:23:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:25:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 19:26:28 IST 2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Tue Jan 21 17:32:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:33:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:34:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:35:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:36:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:37:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:39:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:40:16 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:41:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:42:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:43:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:44:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:47:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:50:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 17:51:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Jan 21 18:07:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:09:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:10:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:11:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:12:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:13:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:14:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:16:12 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:17:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:18:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:20:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:21:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:22:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:25:58 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:34:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:35:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Apr 09 01:42:36 IST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:34:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:35:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:36:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:36:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:37:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:37:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:38:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:39:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:39:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:40:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:41:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:41:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:43:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:46:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:46:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Sat Nov 15 20:48:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 09:48:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:07:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:09:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:10:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:11:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:12:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:13:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:17:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:18:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:19:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:20:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:21:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:22:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:24:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:31:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:32:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:35:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:42:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:43:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:44:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:45:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:46:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:47:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:48:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:49:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:50:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:51:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:52:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:53:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 14:55:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 15:03:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 15:04:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 15:08:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 19:21:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 19:23:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 19:25:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 19:26:28 IST 2026</t>
+    <t>Thu Feb 12 22:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 22:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 22:25:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 22:27:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:06:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:07:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:09:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:10:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:11:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:12:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:13:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:14:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:15:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:16:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:26:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:27:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Feb 22 22:30:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 21:55:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 21:56:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 21:57:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 21:58:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 21:59:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:01:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:02:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:04:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:05:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:06:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:10:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:17:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:18:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sun Mar 01 22:22:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1235,34 +1088,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4684B99E-74C7-4C50-809D-02154653C064}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1318,19 +1171,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -1348,12 +1201,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -1384,12 +1237,12 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -1419,12 +1272,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -1454,12 +1307,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -1502,34 +1355,34 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0998B4B-1379-4C62-AAAC-69FB8C23F4B6}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -1585,19 +1438,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -1615,7 +1468,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
@@ -1649,15 +1502,15 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
     </row>
@@ -1669,49 +1522,49 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1CECF72-ED76-4A08-B368-44E780FE04C9}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5703125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="38.5546875" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.28515625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.85546875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
     <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
     <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.42578125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5703125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
     <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.140625" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.7109375" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.85546875" collapsed="true"/>
-    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="1" width="9.85546875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="29" max="29" style="1" width="15.7109375" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="41" max="41" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.28515625" collapsed="true"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="51" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1863,7 +1716,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>105</v>
       </c>
@@ -1947,7 +1800,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>106</v>
       </c>
@@ -2042,7 +1895,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>107</v>
       </c>
@@ -2178,34 +2031,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCE14908-B016-4D5E-AEA7-D54DB9070BC6}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2261,19 +2114,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -2291,12 +2144,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>265</v>
+        <v>208</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2327,12 +2180,12 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>266</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2362,12 +2215,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2397,12 +2250,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2441,34 +2294,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822FCC47-1993-44A8-9BE0-581A41644C90}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2524,19 +2377,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -2554,12 +2407,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2590,12 +2443,12 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2625,12 +2478,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2660,12 +2513,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2703,34 +2556,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0550F98D-701F-463B-8524-B8E5F73F2D8E}">
   <dimension ref="A1:AC5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2786,19 +2639,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -2816,7 +2669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2" s="1" t="s">
@@ -2848,15 +2701,15 @@
       </c>
       <c r="AB2" s="2"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3"/>
       <c r="B3"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
     </row>
@@ -2868,35 +2721,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30327A80-5D3D-4DEF-87CB-A4BDC28D6002}">
   <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="1" width="15.7109375" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.28515625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" style="1" width="15.6640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" style="1" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="15.140625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.28515625" collapsed="true"/>
-    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" style="1" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="15.109375" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.33203125" collapsed="true"/>
+    <col min="13" max="17" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="1" width="23.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="1" width="28.140625" collapsed="true"/>
-    <col min="30" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="1" width="28.109375" collapsed="true"/>
+    <col min="30" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -2952,19 +2805,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -2985,12 +2838,12 @@
         <v>143</v>
       </c>
     </row>
-    <row ht="30" r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row ht="28.8" r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>111</v>
@@ -3027,12 +2880,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>112</v>
@@ -3068,11 +2921,11 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4"/>
       <c r="B4"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5"/>
       <c r="B5"/>
     </row>
@@ -3084,49 +2937,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB57A2-D7E3-4332-BF3A-D9FD91EC8308}">
   <dimension ref="A1:AY2"/>
-  <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="49.42578125" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="1" width="49.44140625" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="4.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.28515625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="8.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.85546875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
     <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
     <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.42578125" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5703125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.44140625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="5.5546875" collapsed="true"/>
     <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.140625" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.7109375" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.85546875" collapsed="true"/>
-    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="1" width="9.85546875" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.85546875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.42578125" collapsed="true"/>
-    <col min="29" max="29" style="1" width="15.7109375" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.42578125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
-    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.85546875" collapsed="true"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.85546875" collapsed="true"/>
-    <col min="41" max="41" customWidth="true" style="1" width="17.7109375" collapsed="true"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.28515625" collapsed="true"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5703125" collapsed="true"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.140625" collapsed="true"/>
-    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.42578125" collapsed="true"/>
-    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.140625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="6.109375" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="23.88671875" collapsed="true"/>
+    <col min="18" max="23" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="6.88671875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.6640625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="6.44140625" collapsed="true"/>
+    <col min="29" max="29" style="1" width="15.6640625" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.44140625" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="32" max="33" bestFit="true" customWidth="true" style="1" width="9.6640625" collapsed="true"/>
+    <col min="34" max="39" bestFit="true" customWidth="true" style="1" width="7.88671875" collapsed="true"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="8.88671875" collapsed="true"/>
+    <col min="41" max="41" customWidth="true" style="1" width="17.6640625" collapsed="true"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="17.33203125" collapsed="true"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="8.109375" collapsed="true"/>
+    <col min="45" max="46" bestFit="true" customWidth="true" style="1" width="7.44140625" collapsed="true"/>
+    <col min="47" max="48" bestFit="true" customWidth="true" style="1" width="9.109375" collapsed="true"/>
     <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
     <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.0" collapsed="true"/>
-    <col min="51" max="16384" style="1" width="15.7109375" collapsed="true"/>
+    <col min="51" max="16384" style="1" width="15.6640625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3278,7 +3131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>116</v>
       </c>
@@ -3320,152 +3173,152 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6029C9A2-9E58-4FB9-972D-7B9E934718A7}">
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="56.42578125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="56.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>100</v>
       </c>
       <c r="B1" s="3"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>101</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>102</v>
       </c>
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>103</v>
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>111</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>112</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>113</v>
       </c>
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>114</v>
       </c>
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>115</v>
       </c>
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>121</v>
       </c>
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>139</v>
       </c>
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>140</v>
       </c>
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>155</v>
       </c>
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>158</v>
       </c>
@@ -3481,29 +3334,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54F5F0A8-DFAA-493B-B07B-97C59CBB0D66}">
   <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.85546875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.42578125" collapsed="true"/>
-    <col min="9" max="17" bestFit="true" customWidth="true" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5703125" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.28515625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3559,19 +3412,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -3589,12 +3442,12 @@
         <v>16</v>
       </c>
     </row>
-    <row customFormat="1" ht="45" r="2" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="28.8" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -3633,29 +3486,29 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133992E5-F2D4-42EB-B2FB-D66167060930}">
   <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.85546875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="19.28515625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.88671875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.33203125" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.140625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.7109375" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.42578125" collapsed="true"/>
-    <col min="9" max="17" bestFit="true" customWidth="true" width="7.85546875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.85546875" collapsed="true"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5703125" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.28515625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5703125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
-    <col min="23" max="24" bestFit="true" customWidth="true" width="7.42578125" collapsed="true"/>
-    <col min="25" max="26" bestFit="true" customWidth="true" width="6.42578125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.44140625" collapsed="true"/>
+    <col min="9" max="17" bestFit="true" customWidth="true" width="7.88671875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="8.5546875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.33203125" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="6.5546875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
+    <col min="23" max="24" bestFit="true" customWidth="true" width="7.44140625" collapsed="true"/>
+    <col min="25" max="26" bestFit="true" customWidth="true" width="6.44140625" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" width="6.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="8.140625" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="8.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>131</v>
       </c>
@@ -3711,19 +3564,19 @@
         <v>26</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>76</v>
@@ -3741,12 +3594,12 @@
         <v>16</v>
       </c>
     </row>
-    <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="2" s="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>264</v>
+        <v>219</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>

--- a/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
+++ b/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="236">
   <si>
     <t>Notes</t>
   </si>
@@ -703,6 +703,54 @@
   </si>
   <si>
     <t>Sun Mar 01 22:22:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:44:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:45:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:46:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:48:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:49:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:50:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:54:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 19:59:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 20:07:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 20:08:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 20:11:52 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1254,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -1242,7 +1290,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -1277,7 +1325,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -1312,7 +1360,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2149,7 +2197,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2185,7 +2233,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2220,7 +2268,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2255,7 +2303,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2412,7 +2460,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2448,7 +2496,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2483,7 +2531,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2518,7 +2566,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2843,7 +2891,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>111</v>
@@ -2885,7 +2933,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>112</v>
@@ -3447,7 +3495,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -3599,7 +3647,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>

--- a/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
+++ b/KatalonData/IWPTestData/VRelay30PayNowCC.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="252">
   <si>
     <t>Notes</t>
   </si>
@@ -751,6 +751,54 @@
   </si>
   <si>
     <t>Tue May 05 20:11:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:08:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:09:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:11:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:11:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:13:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:14:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:15:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:17:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:18:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:19:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:22:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:28:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:28:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 23:32:19 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1302,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -1290,7 +1338,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -1325,7 +1373,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -1360,7 +1408,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2197,7 +2245,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2233,7 +2281,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2268,7 +2316,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2303,7 +2351,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2460,7 +2508,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>124</v>
@@ -2496,7 +2544,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>124</v>
@@ -2531,7 +2579,7 @@
         <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>124</v>
@@ -2566,7 +2614,7 @@
         <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>124</v>
@@ -2891,7 +2939,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>111</v>
@@ -2933,7 +2981,7 @@
         <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>112</v>
@@ -3495,7 +3543,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>151</v>
@@ -3647,7 +3695,7 @@
         <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>153</v>
